--- a/Result/profitability/2429.xlsx
+++ b/Result/profitability/2429.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.395</v>
+        <v>-0.37625</v>
       </c>
       <c r="N2" t="n">
-        <v>4.24</v>
+        <v>4.16625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3625</v>
+        <v>-0.3137500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7425</v>
+        <v>4.945</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.26</v>
+        <v>-0.27125</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4375</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.36</v>
+        <v>-0.33625</v>
       </c>
       <c r="N5" t="n">
-        <v>3.135</v>
+        <v>4.063750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.25125</v>
+        <v>-0.26125</v>
       </c>
       <c r="N6" t="n">
-        <v>5.61875</v>
+        <v>5.9975</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.24</v>
+        <v>-0.2187500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>6.91375</v>
+        <v>7.01375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.20875</v>
+        <v>-0.1912500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.60625</v>
+        <v>7.70125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1375</v>
+        <v>-0.1375000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.115000000000001</v>
+        <v>6.115</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>-0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1675</v>
+        <v>-0.1675000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98625</v>
+        <v>2.986250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>-0.32</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2225000000000001</v>
+        <v>-0.2225</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5887500000000006</v>
+        <v>0.5887500000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.15</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2974999999999994</v>
+        <v>-0.2974999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9348,27 +9348,27 @@
         <v>-2.43</v>
       </c>
       <c r="G71" t="n">
-        <v>-46</v>
+        <v>-48</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-55.57%</t>
+          <t>-58.15%</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="K71" t="n">
-        <v>-41</v>
+        <v>-43</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.3800000000000001</v>
+        <v>-0.3825000000000001</v>
       </c>
       <c r="N71" t="n">
         <v>1.33875</v>
@@ -9398,10 +9398,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="X71" t="n">
-        <v>1.181818181818182</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="Y71" t="n">
         <v>-9.33</v>
@@ -9410,10 +9410,10 @@
         <v>-1.352173913043478</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AB71" t="n">
-        <v>-0.5051546391752577</v>
+        <v>-0.4845360824742267</v>
       </c>
       <c r="AC71" t="n">
         <v>-2.14</v>
@@ -9475,24 +9475,24 @@
         <v>1.97</v>
       </c>
       <c r="G72" t="n">
-        <v>-31</v>
+        <v>-29</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-26.06%</t>
+          <t>-24.27%</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>15</v>
       </c>
       <c r="J72" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="K72" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L72" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="M72" t="n">
         <v>-0.3925</v>
@@ -9525,10 +9525,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.5208333333333333</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="Y72" t="n">
         <v>4.4</v>
@@ -9537,10 +9537,10 @@
         <v>-1.810699588477366</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.5</v>
+        <v>-0.5434782608695652</v>
       </c>
       <c r="AC72" t="n">
         <v>-3.62</v>
@@ -9652,10 +9652,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="X73" t="n">
-        <v>1.08695652173913</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="Y73" t="n">
         <v>2.23</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>91</v>
+      </c>
+      <c r="D75" t="n">
+        <v>87</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-28.93%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.41625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.60625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3111111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1792452830188678</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.05761316872428</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
